--- a/research/traditional_assets/database/data/indonesia/indonesia_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_investments_asset_management.xlsx
@@ -588,121 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.274</v>
+        <v>0.3025</v>
       </c>
       <c r="E2">
-        <v>0.2125</v>
+        <v>0.4794999999999999</v>
+      </c>
+      <c r="F2">
+        <v>0.168</v>
       </c>
       <c r="G2">
-        <v>0.393630343166767</v>
+        <v>1.282020343739039</v>
       </c>
       <c r="H2">
-        <v>0.393630343166767</v>
+        <v>1.282020343739039</v>
       </c>
       <c r="I2">
-        <v>0.9484708007224564</v>
+        <v>0.9354612416695897</v>
       </c>
       <c r="J2">
-        <v>0.7890905657932125</v>
+        <v>0.8127032580186958</v>
       </c>
       <c r="K2">
-        <v>1533.19</v>
+        <v>1230.46</v>
       </c>
       <c r="L2">
-        <v>0.9230523780854907</v>
+        <v>0.86317783233953</v>
       </c>
       <c r="M2">
-        <v>33.09</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="N2">
-        <v>0.0104256592835313</v>
+        <v>0.03366105040020467</v>
       </c>
       <c r="O2">
-        <v>0.02158245227271244</v>
+        <v>0.07485005607658923</v>
       </c>
       <c r="P2">
-        <v>26.2</v>
+        <v>65.134</v>
       </c>
       <c r="Q2">
-        <v>0.008254828444500456</v>
+        <v>0.02380541646869632</v>
       </c>
       <c r="R2">
-        <v>0.01708855393004129</v>
+        <v>0.05293467483705281</v>
       </c>
       <c r="S2">
-        <v>6.89</v>
+        <v>26.966</v>
       </c>
       <c r="T2">
-        <v>0.2082200060441221</v>
+        <v>0.2927904451682953</v>
       </c>
       <c r="U2">
-        <v>57.2</v>
+        <v>145</v>
       </c>
       <c r="V2">
-        <v>0.01802199187119947</v>
+        <v>0.05299513906655458</v>
       </c>
       <c r="W2">
-        <v>0.3459595959595959</v>
+        <v>0.3795348837209302</v>
       </c>
       <c r="X2">
-        <v>0.05997778527968038</v>
+        <v>0.09337082015396073</v>
       </c>
       <c r="Y2">
-        <v>0.2859818106799155</v>
+        <v>0.2861640635669696</v>
       </c>
       <c r="Z2">
-        <v>0.8727837545570242</v>
+        <v>0.40724731668157</v>
       </c>
       <c r="AA2">
-        <v>0.8573001305728439</v>
+        <v>0.3538189856397652</v>
       </c>
       <c r="AB2">
-        <v>0.0573934138784465</v>
+        <v>0.09209852650111353</v>
       </c>
       <c r="AC2">
-        <v>0.7999889273853692</v>
+        <v>0.2617204591386517</v>
       </c>
       <c r="AD2">
-        <v>300.53</v>
+        <v>163.43</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>300.53</v>
+        <v>163.43</v>
       </c>
       <c r="AG2">
-        <v>243.33</v>
+        <v>18.43000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.08649764133973054</v>
+        <v>0.05636430731877236</v>
       </c>
       <c r="AI2">
-        <v>0.08392278199289031</v>
+        <v>0.03729379790654529</v>
       </c>
       <c r="AJ2">
-        <v>0.0712067961477571</v>
+        <v>0.006690796615030517</v>
       </c>
       <c r="AK2">
-        <v>0.06905270685589258</v>
+        <v>0.004349539675684352</v>
       </c>
       <c r="AL2">
-        <v>13.59</v>
+        <v>13.081</v>
       </c>
       <c r="AM2">
-        <v>12.917</v>
+        <v>12.659</v>
       </c>
       <c r="AN2">
-        <v>0.190749720727125</v>
+        <v>0.1225479904019196</v>
       </c>
       <c r="AO2">
-        <v>115.9242089771891</v>
+        <v>101.9417475728155</v>
       </c>
       <c r="AP2">
-        <v>0.1544442469787753</v>
+        <v>0.01381973605278945</v>
       </c>
       <c r="AQ2">
-        <v>121.9640783463653</v>
+        <v>105.3400742554704</v>
       </c>
     </row>
     <row r="3">
@@ -721,116 +724,119 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="F3">
+        <v>0.168</v>
+      </c>
       <c r="G3">
-        <v>0.3515151515151514</v>
+        <v>0.2869257950530035</v>
       </c>
       <c r="H3">
-        <v>0.3515151515151514</v>
+        <v>0.2869257950530035</v>
       </c>
       <c r="I3">
-        <v>0.3467532467532467</v>
+        <v>0.3568904593639576</v>
       </c>
       <c r="J3">
-        <v>0.2745965017641318</v>
+        <v>0.2796785811361783</v>
       </c>
       <c r="K3">
-        <v>6.85</v>
+        <v>8.16</v>
       </c>
       <c r="L3">
-        <v>0.2965367965367965</v>
+        <v>0.288339222614841</v>
       </c>
       <c r="M3">
-        <v>5.5</v>
+        <v>8.311</v>
       </c>
       <c r="N3">
-        <v>0.01890684083877621</v>
+        <v>0.04385751978891821</v>
       </c>
       <c r="O3">
-        <v>0.8029197080291971</v>
+        <v>1.018504901960784</v>
       </c>
       <c r="P3">
-        <v>5.5</v>
+        <v>7.81</v>
       </c>
       <c r="Q3">
-        <v>0.01890684083877621</v>
+        <v>0.04121372031662269</v>
       </c>
       <c r="R3">
-        <v>0.8029197080291971</v>
+        <v>0.9571078431372548</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.5010000000000003</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.06028155456623756</v>
       </c>
       <c r="U3">
-        <v>18</v>
+        <v>12.4</v>
       </c>
       <c r="V3">
-        <v>0.0618769336541767</v>
+        <v>0.06543535620052771</v>
       </c>
       <c r="W3">
-        <v>0.3459595959595959</v>
+        <v>0.3795348837209302</v>
       </c>
       <c r="X3">
-        <v>0.05754919795174415</v>
+        <v>0.09144334494578427</v>
       </c>
       <c r="Y3">
-        <v>0.2884103980078518</v>
+        <v>0.288091538775146</v>
       </c>
       <c r="Z3">
-        <v>4.437187860161352</v>
+        <v>5.740365111561867</v>
       </c>
       <c r="AA3">
-        <v>1.218436264070581</v>
+        <v>1.605457169605243</v>
       </c>
       <c r="AB3">
-        <v>0.0573934138784465</v>
+        <v>0.09124061663144774</v>
       </c>
       <c r="AC3">
-        <v>1.161042850192134</v>
+        <v>1.514216552973795</v>
       </c>
       <c r="AD3">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="AG3">
-        <v>-16.57</v>
+        <v>-11.17</v>
       </c>
       <c r="AH3">
-        <v>0.004891731946772483</v>
+        <v>0.006448906831646831</v>
       </c>
       <c r="AI3">
-        <v>0.06236371565634539</v>
+        <v>0.05340859748154581</v>
       </c>
       <c r="AJ3">
-        <v>-0.06040170597455619</v>
+        <v>-0.06263668479784669</v>
       </c>
       <c r="AK3">
-        <v>-3.36105476673428</v>
+        <v>-1.050799623706491</v>
       </c>
       <c r="AL3">
-        <v>0.09</v>
+        <v>0.081</v>
       </c>
       <c r="AM3">
-        <v>-0.5830000000000001</v>
+        <v>-0.341</v>
       </c>
       <c r="AN3">
-        <v>0.1761083743842365</v>
+        <v>0.1217821782178218</v>
       </c>
       <c r="AO3">
-        <v>89</v>
+        <v>124.6913580246914</v>
       </c>
       <c r="AP3">
-        <v>-2.04064039408867</v>
+        <v>-1.105940594059406</v>
       </c>
       <c r="AQ3">
-        <v>-13.73927958833619</v>
+        <v>-29.61876832844575</v>
       </c>
     </row>
     <row r="4">
@@ -850,121 +856,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.261</v>
+        <v>0.347</v>
       </c>
       <c r="E4">
-        <v>0.292</v>
+        <v>0.426</v>
       </c>
       <c r="G4">
-        <v>0.4083865663145911</v>
+        <v>1.362132215317811</v>
       </c>
       <c r="H4">
-        <v>0.4083865663145911</v>
+        <v>1.362132215317811</v>
       </c>
       <c r="I4">
-        <v>0.9913351464170516</v>
+        <v>0.9907913453619825</v>
       </c>
       <c r="J4">
-        <v>0.9663942968313072</v>
+        <v>0.8955273225667096</v>
       </c>
       <c r="K4">
-        <v>1519</v>
+        <v>1179.9</v>
       </c>
       <c r="L4">
-        <v>0.9607235468977294</v>
+        <v>0.8833570412517782</v>
       </c>
       <c r="M4">
-        <v>20.7</v>
+        <v>53.265</v>
       </c>
       <c r="N4">
-        <v>0.007824607824607824</v>
+        <v>0.02433747601206251</v>
       </c>
       <c r="O4">
-        <v>0.01362738643844635</v>
+        <v>0.04514365624205441</v>
       </c>
       <c r="P4">
-        <v>20.7</v>
+        <v>53.2</v>
       </c>
       <c r="Q4">
-        <v>0.007824607824607824</v>
+        <v>0.0243077766608791</v>
       </c>
       <c r="R4">
-        <v>0.01362738643844635</v>
+        <v>0.04508856682769726</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>0.06499999999999773</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.001220313526706049</v>
       </c>
       <c r="U4">
-        <v>27.8</v>
+        <v>71</v>
       </c>
       <c r="V4">
-        <v>0.01050841050841051</v>
+        <v>0.03244082975418076</v>
       </c>
       <c r="W4">
-        <v>0.9512179848456384</v>
+        <v>0.3731617065688352</v>
       </c>
       <c r="X4">
-        <v>0.05997778527968038</v>
+        <v>0.09337082015396073</v>
       </c>
       <c r="Y4">
-        <v>0.891240199565958</v>
+        <v>0.2797908864148745</v>
       </c>
       <c r="Z4">
-        <v>0.8871121584469506</v>
+        <v>0.395095690241666</v>
       </c>
       <c r="AA4">
-        <v>0.8573001305728439</v>
+        <v>0.3538189856397652</v>
       </c>
       <c r="AB4">
-        <v>0.05731120318747476</v>
+        <v>0.09209852650111353</v>
       </c>
       <c r="AC4">
-        <v>0.7999889273853692</v>
+        <v>0.2617204591386517</v>
       </c>
       <c r="AD4">
-        <v>246.6</v>
+        <v>109</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>246.6</v>
+        <v>109</v>
       </c>
       <c r="AG4">
-        <v>218.8</v>
+        <v>38</v>
       </c>
       <c r="AH4">
-        <v>0.08526676117699941</v>
+        <v>0.0474408077994429</v>
       </c>
       <c r="AI4">
-        <v>0.07232095724089389</v>
+        <v>0.0259332397516119</v>
       </c>
       <c r="AJ4">
-        <v>0.07638864644066612</v>
+        <v>0.01706637923291117</v>
       </c>
       <c r="AK4">
-        <v>0.06469544648137196</v>
+        <v>0.009196292442099657</v>
       </c>
       <c r="AL4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AM4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AN4">
-        <v>0.1573306112032666</v>
+        <v>0.08235738571968267</v>
       </c>
       <c r="AO4">
-        <v>116.1037037037037</v>
+        <v>101.8</v>
       </c>
       <c r="AP4">
-        <v>0.139594232486921</v>
+        <v>0.02871174914998111</v>
       </c>
       <c r="AQ4">
-        <v>116.1037037037037</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="5">
@@ -984,10 +990,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.287</v>
+        <v>0.258</v>
       </c>
       <c r="E5">
-        <v>0.133</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1002,85 +1008,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>7.34</v>
+        <v>42.4</v>
       </c>
       <c r="L5">
-        <v>0.1292253521126761</v>
+        <v>0.6894308943089431</v>
       </c>
       <c r="M5">
-        <v>6.89</v>
+        <v>30.524</v>
       </c>
       <c r="N5">
-        <v>0.02901052631578947</v>
+        <v>0.08526256983240223</v>
       </c>
       <c r="O5">
-        <v>0.938692098092643</v>
+        <v>0.7199056603773585</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>4.124</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.0115195530726257</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.09726415094339622</v>
       </c>
       <c r="S5">
-        <v>6.89</v>
+        <v>26.4</v>
       </c>
       <c r="T5">
-        <v>1</v>
+        <v>0.8648931987943913</v>
       </c>
       <c r="U5">
-        <v>11.4</v>
+        <v>61.6</v>
       </c>
       <c r="V5">
-        <v>0.048</v>
+        <v>0.1720670391061453</v>
       </c>
       <c r="W5">
-        <v>0.1090638930163447</v>
+        <v>0.5760869565217391</v>
       </c>
       <c r="X5">
-        <v>0.06349384671291905</v>
+        <v>0.09776754303192817</v>
       </c>
       <c r="Y5">
-        <v>0.04557004630342568</v>
+        <v>0.478319413489811</v>
       </c>
       <c r="Z5">
-        <v>0.4913494809688581</v>
+        <v>0.5361813426329556</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05755426852094119</v>
+        <v>0.09414688035893828</v>
       </c>
       <c r="AC5">
-        <v>-0.05755426852094119</v>
+        <v>-0.09414688035893828</v>
       </c>
       <c r="AD5">
-        <v>52.5</v>
+        <v>53.2</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>52.5</v>
+        <v>53.2</v>
       </c>
       <c r="AG5">
-        <v>41.1</v>
+        <v>-8.399999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.1810344827586207</v>
+        <v>0.1293774319066148</v>
       </c>
       <c r="AI5">
-        <v>0.354012137559002</v>
+        <v>0.3408071748878924</v>
       </c>
       <c r="AJ5">
-        <v>0.1475233309404164</v>
+        <v>-0.02402745995423341</v>
       </c>
       <c r="AK5">
-        <v>0.3002191380569759</v>
+        <v>-0.08888888888888888</v>
       </c>
       <c r="AL5">
         <v>0</v>

--- a/research/traditional_assets/database/data/indonesia/indonesia_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.3025</v>
+        <v>0.0587</v>
       </c>
       <c r="E2">
-        <v>0.4794999999999999</v>
-      </c>
-      <c r="F2">
-        <v>0.168</v>
+        <v>0.0673</v>
       </c>
       <c r="G2">
-        <v>1.282020343739039</v>
+        <v>5.221028984001661</v>
       </c>
       <c r="H2">
-        <v>1.282020343739039</v>
+        <v>5.221028984001661</v>
       </c>
       <c r="I2">
-        <v>0.9354612416695897</v>
+        <v>-11.67182630376065</v>
       </c>
       <c r="J2">
-        <v>0.8127032580186958</v>
+        <v>-10.25459541546266</v>
       </c>
       <c r="K2">
-        <v>1230.46</v>
+        <v>-837.456</v>
       </c>
       <c r="L2">
-        <v>0.86317783233953</v>
+        <v>-10.87492208601704</v>
       </c>
       <c r="M2">
-        <v>92.09999999999999</v>
+        <v>87.485</v>
       </c>
       <c r="N2">
-        <v>0.03366105040020467</v>
+        <v>0.04490324898629575</v>
       </c>
       <c r="O2">
-        <v>0.07485005607658923</v>
+        <v>-0.1044651898129573</v>
       </c>
       <c r="P2">
-        <v>65.134</v>
+        <v>76.53</v>
       </c>
       <c r="Q2">
-        <v>0.02380541646869632</v>
+        <v>0.03928039829595031</v>
       </c>
       <c r="R2">
-        <v>0.05293467483705281</v>
+        <v>-0.09138390554250014</v>
       </c>
       <c r="S2">
-        <v>26.966</v>
+        <v>10.955</v>
       </c>
       <c r="T2">
-        <v>0.2927904451682953</v>
+        <v>0.1252214665371206</v>
       </c>
       <c r="U2">
-        <v>145</v>
+        <v>87.19</v>
       </c>
       <c r="V2">
-        <v>0.05299513906655458</v>
+        <v>0.04475183493301853</v>
       </c>
       <c r="W2">
-        <v>0.3795348837209302</v>
+        <v>0.03119193661746853</v>
       </c>
       <c r="X2">
-        <v>0.09337082015396073</v>
+        <v>0.07714082213457105</v>
       </c>
       <c r="Y2">
-        <v>0.2861640635669696</v>
+        <v>-0.04594888551710252</v>
       </c>
       <c r="Z2">
-        <v>0.40724731668157</v>
+        <v>0.01819348915579876</v>
       </c>
       <c r="AA2">
-        <v>0.3538189856397652</v>
+        <v>-0.01851663751105093</v>
       </c>
       <c r="AB2">
-        <v>0.09209852650111353</v>
+        <v>0.07669533718168953</v>
       </c>
       <c r="AC2">
-        <v>0.2617204591386517</v>
+        <v>-0.09579883281701435</v>
       </c>
       <c r="AD2">
-        <v>163.43</v>
+        <v>100.575</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>163.43</v>
+        <v>100.575</v>
       </c>
       <c r="AG2">
-        <v>18.43000000000001</v>
+        <v>13.38500000000001</v>
       </c>
       <c r="AH2">
-        <v>0.05636430731877236</v>
+        <v>0.04908791409920078</v>
       </c>
       <c r="AI2">
-        <v>0.03729379790654529</v>
+        <v>0.02974205806465922</v>
       </c>
       <c r="AJ2">
-        <v>0.006690796615030517</v>
+        <v>0.006823215755842557</v>
       </c>
       <c r="AK2">
-        <v>0.004349539675684352</v>
+        <v>0.004062973817571414</v>
       </c>
       <c r="AL2">
-        <v>13.081</v>
+        <v>7.035</v>
       </c>
       <c r="AM2">
-        <v>12.659</v>
+        <v>6.271</v>
       </c>
       <c r="AN2">
-        <v>0.1225479904019196</v>
+        <v>-0.1119197449465022</v>
       </c>
       <c r="AO2">
-        <v>101.9417475728155</v>
+        <v>-127.76460554371</v>
       </c>
       <c r="AP2">
-        <v>0.01381973605278945</v>
+        <v>-0.01489481268813256</v>
       </c>
       <c r="AQ2">
-        <v>105.3400742554704</v>
+        <v>-143.3302503587944</v>
       </c>
     </row>
     <row r="3">
@@ -724,119 +721,122 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="F3">
-        <v>0.168</v>
+      <c r="D3">
+        <v>0.0587</v>
+      </c>
+      <c r="E3">
+        <v>0.0673</v>
       </c>
       <c r="G3">
-        <v>0.2869257950530035</v>
+        <v>0.3398148148148148</v>
       </c>
       <c r="H3">
-        <v>0.2869257950530035</v>
+        <v>0.3398148148148148</v>
       </c>
       <c r="I3">
-        <v>0.3568904593639576</v>
+        <v>0.3361111111111111</v>
       </c>
       <c r="J3">
-        <v>0.2796785811361783</v>
+        <v>0.2668990418990419</v>
       </c>
       <c r="K3">
-        <v>8.16</v>
+        <v>6.17</v>
       </c>
       <c r="L3">
-        <v>0.288339222614841</v>
+        <v>0.2856481481481482</v>
       </c>
       <c r="M3">
-        <v>8.311</v>
+        <v>7.503</v>
       </c>
       <c r="N3">
-        <v>0.04385751978891821</v>
+        <v>0.05321276595744681</v>
       </c>
       <c r="O3">
-        <v>1.018504901960784</v>
+        <v>1.216045380875203</v>
       </c>
       <c r="P3">
-        <v>7.81</v>
+        <v>7.16</v>
       </c>
       <c r="Q3">
-        <v>0.04121372031662269</v>
+        <v>0.05078014184397163</v>
       </c>
       <c r="R3">
-        <v>0.9571078431372548</v>
+        <v>1.160453808752026</v>
       </c>
       <c r="S3">
-        <v>0.5010000000000003</v>
+        <v>0.343</v>
       </c>
       <c r="T3">
-        <v>0.06028155456623756</v>
+        <v>0.04571504731440756</v>
       </c>
       <c r="U3">
-        <v>12.4</v>
+        <v>9.49</v>
       </c>
       <c r="V3">
-        <v>0.06543535620052771</v>
+        <v>0.0673049645390071</v>
       </c>
       <c r="W3">
-        <v>0.3795348837209302</v>
+        <v>0.2980676328502416</v>
       </c>
       <c r="X3">
-        <v>0.09144334494578427</v>
+        <v>0.07677324150816742</v>
       </c>
       <c r="Y3">
-        <v>0.288091538775146</v>
+        <v>0.2212943913420742</v>
       </c>
       <c r="Z3">
-        <v>5.740365111561867</v>
+        <v>2.099125364431487</v>
       </c>
       <c r="AA3">
-        <v>1.605457169605243</v>
+        <v>0.5602545485927412</v>
       </c>
       <c r="AB3">
-        <v>0.09124061663144774</v>
+        <v>0.07657259998123825</v>
       </c>
       <c r="AC3">
-        <v>1.514216552973795</v>
+        <v>0.4836819486115029</v>
       </c>
       <c r="AD3">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AG3">
-        <v>-11.17</v>
+        <v>-8.370000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.006448906831646831</v>
+        <v>0.007880664227413453</v>
       </c>
       <c r="AI3">
-        <v>0.05340859748154581</v>
+        <v>0.05458089668615985</v>
       </c>
       <c r="AJ3">
-        <v>-0.06263668479784669</v>
+        <v>-0.06310789414159694</v>
       </c>
       <c r="AK3">
-        <v>-1.050799623706491</v>
+        <v>-0.7588395285584771</v>
       </c>
       <c r="AL3">
-        <v>0.081</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AM3">
-        <v>-0.341</v>
+        <v>-0.204</v>
       </c>
       <c r="AN3">
-        <v>0.1217821782178218</v>
+        <v>0.1525885558583106</v>
       </c>
       <c r="AO3">
-        <v>124.6913580246914</v>
+        <v>105.2173913043478</v>
       </c>
       <c r="AP3">
-        <v>-1.105940594059406</v>
+        <v>-1.140326975476839</v>
       </c>
       <c r="AQ3">
-        <v>-29.61876832844575</v>
+        <v>-35.58823529411764</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PT Saratoga Investama Sedaya Tbk (IDX:SRTG)</t>
+          <t>PT Batavia Prosperindo Internasional Tbk (IDX:BPII)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,121 +856,109 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.347</v>
+        <v>0.231</v>
       </c>
       <c r="E4">
-        <v>0.426</v>
+        <v>-0.00375</v>
       </c>
       <c r="G4">
-        <v>1.362132215317811</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>1.362132215317811</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.9907913453619825</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>0.8955273225667096</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>1179.9</v>
+        <v>5.26</v>
       </c>
       <c r="L4">
-        <v>0.8833570412517782</v>
+        <v>0.0954627949183303</v>
       </c>
       <c r="M4">
-        <v>53.265</v>
+        <v>14.17</v>
       </c>
       <c r="N4">
-        <v>0.02433747601206251</v>
+        <v>0.04282260501662134</v>
       </c>
       <c r="O4">
-        <v>0.04514365624205441</v>
+        <v>2.693916349809886</v>
       </c>
       <c r="P4">
-        <v>53.2</v>
+        <v>3.87</v>
       </c>
       <c r="Q4">
-        <v>0.0243077766608791</v>
+        <v>0.01169537624660018</v>
       </c>
       <c r="R4">
-        <v>0.04508856682769726</v>
+        <v>0.7357414448669202</v>
       </c>
       <c r="S4">
-        <v>0.06499999999999773</v>
+        <v>10.3</v>
       </c>
       <c r="T4">
-        <v>0.001220313526706049</v>
+        <v>0.7268877911079745</v>
       </c>
       <c r="U4">
-        <v>71</v>
+        <v>24.1</v>
       </c>
       <c r="V4">
-        <v>0.03244082975418076</v>
+        <v>0.07283167119975824</v>
       </c>
       <c r="W4">
-        <v>0.3731617065688352</v>
+        <v>0.05595744680851063</v>
       </c>
       <c r="X4">
-        <v>0.09337082015396073</v>
+        <v>0.08115642317490987</v>
       </c>
       <c r="Y4">
-        <v>0.2797908864148745</v>
+        <v>-0.02519897636639924</v>
       </c>
       <c r="Z4">
-        <v>0.395095690241666</v>
+        <v>0.6436915887850468</v>
       </c>
       <c r="AA4">
-        <v>0.3538189856397652</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.09209852650111353</v>
+        <v>0.07800717533596767</v>
       </c>
       <c r="AC4">
-        <v>0.2617204591386517</v>
+        <v>-0.07800717533596767</v>
       </c>
       <c r="AD4">
-        <v>109</v>
+        <v>51.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>109</v>
+        <v>51.9</v>
       </c>
       <c r="AG4">
-        <v>38</v>
+        <v>27.8</v>
       </c>
       <c r="AH4">
-        <v>0.0474408077994429</v>
+        <v>0.1355799373040752</v>
       </c>
       <c r="AI4">
-        <v>0.0259332397516119</v>
+        <v>0.3293147208121828</v>
       </c>
       <c r="AJ4">
-        <v>0.01706637923291117</v>
+        <v>0.07750209088374686</v>
       </c>
       <c r="AK4">
-        <v>0.009196292442099657</v>
+        <v>0.2082397003745318</v>
       </c>
       <c r="AL4">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>13</v>
-      </c>
-      <c r="AN4">
-        <v>0.08235738571968267</v>
-      </c>
-      <c r="AO4">
-        <v>101.8</v>
-      </c>
-      <c r="AP4">
-        <v>0.02871174914998111</v>
-      </c>
-      <c r="AQ4">
-        <v>101.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -981,7 +969,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PT Batavia Prosperindo Internasional Tbk (IDX:BPII)</t>
+          <t>PT Buana Artha Anugerah Tbk (IDX:STAR)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,109 +978,231 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.258</v>
+        <v>-0.485</v>
       </c>
       <c r="E5">
-        <v>0.5329999999999999</v>
+        <v>0.529</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>-0.5811688311688311</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>-0.5811688311688311</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>-0.5974025974025974</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>-0.5811097992916174</v>
       </c>
       <c r="K5">
-        <v>42.4</v>
+        <v>0.214</v>
       </c>
       <c r="L5">
-        <v>0.6894308943089431</v>
+        <v>0.6948051948051948</v>
       </c>
       <c r="M5">
-        <v>30.524</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.08526256983240223</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.7199056603773585</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>4.124</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.0115195530726257</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.09726415094339622</v>
+        <v>-0</v>
       </c>
       <c r="S5">
-        <v>26.4</v>
-      </c>
-      <c r="T5">
-        <v>0.8648931987943913</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>61.6</v>
+        <v>16.3</v>
       </c>
       <c r="V5">
-        <v>0.1720670391061453</v>
+        <v>0.4880239520958084</v>
       </c>
       <c r="W5">
-        <v>0.5760869565217391</v>
+        <v>0.006426426426426427</v>
       </c>
       <c r="X5">
-        <v>0.09776754303192817</v>
+        <v>0.0765878913948506</v>
       </c>
       <c r="Y5">
-        <v>0.478319413489811</v>
+        <v>-0.07016146496842418</v>
       </c>
       <c r="Z5">
-        <v>0.5361813426329556</v>
+        <v>0.06372853300227604</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>-0.03703327502210185</v>
       </c>
       <c r="AB5">
-        <v>0.09414688035893828</v>
+        <v>0.07655721527595917</v>
       </c>
       <c r="AC5">
-        <v>-0.09414688035893828</v>
+        <v>-0.113590490298061</v>
       </c>
       <c r="AD5">
-        <v>53.2</v>
+        <v>0.055</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>53.2</v>
+        <v>0.055</v>
       </c>
       <c r="AG5">
-        <v>-8.399999999999999</v>
+        <v>-16.245</v>
       </c>
       <c r="AH5">
-        <v>0.1293774319066148</v>
+        <v>0.001643999402182036</v>
       </c>
       <c r="AI5">
-        <v>0.3408071748878924</v>
+        <v>0.001663893510815308</v>
       </c>
       <c r="AJ5">
-        <v>-0.02402745995423341</v>
+        <v>-0.9469542407461383</v>
       </c>
       <c r="AK5">
-        <v>-0.08888888888888888</v>
+        <v>-0.9695613249776187</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>-0.435</v>
+      </c>
+      <c r="AN5">
+        <v>-0.3142857142857143</v>
+      </c>
+      <c r="AO5">
+        <v>-3.285714285714286</v>
+      </c>
+      <c r="AP5">
+        <v>92.82857142857144</v>
+      </c>
+      <c r="AQ5">
+        <v>0.4229885057471264</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PT Saratoga Investama Sedaya Tbk (IDX:SRTG)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K6">
+        <v>-849.1</v>
+      </c>
+      <c r="M6">
+        <v>65.812</v>
+      </c>
+      <c r="N6">
+        <v>0.04560776160776161</v>
+      </c>
+      <c r="O6">
+        <v>-0.07750794959368743</v>
+      </c>
+      <c r="P6">
+        <v>65.5</v>
+      </c>
+      <c r="Q6">
+        <v>0.04539154539154539</v>
+      </c>
+      <c r="R6">
+        <v>-0.07714050170769049</v>
+      </c>
+      <c r="S6">
+        <v>0.3119999999999976</v>
+      </c>
+      <c r="T6">
+        <v>0.004740776758038012</v>
+      </c>
+      <c r="U6">
+        <v>37.3</v>
+      </c>
+      <c r="V6">
+        <v>0.02584892584892585</v>
+      </c>
+      <c r="W6">
+        <v>-0.2074010747435271</v>
+      </c>
+      <c r="X6">
+        <v>0.07750840276097468</v>
+      </c>
+      <c r="Y6">
+        <v>-0.2849094775045018</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>-0.2192400774443369</v>
+      </c>
+      <c r="AB6">
+        <v>0.07681807438214081</v>
+      </c>
+      <c r="AC6">
+        <v>-0.2960581518264777</v>
+      </c>
+      <c r="AD6">
+        <v>47.5</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>47.5</v>
+      </c>
+      <c r="AG6">
+        <v>10.2</v>
+      </c>
+      <c r="AH6">
+        <v>0.03186850050318685</v>
+      </c>
+      <c r="AI6">
+        <v>0.01498233661367651</v>
+      </c>
+      <c r="AJ6">
+        <v>0.007018992568125518</v>
+      </c>
+      <c r="AK6">
+        <v>0.003255561584373306</v>
+      </c>
+      <c r="AL6">
+        <v>6.91</v>
+      </c>
+      <c r="AM6">
+        <v>6.91</v>
+      </c>
+      <c r="AN6">
+        <v>-0.05243983219253699</v>
+      </c>
+      <c r="AO6">
+        <v>-131.0998552821997</v>
+      </c>
+      <c r="AP6">
+        <v>-0.01126076396555531</v>
+      </c>
+      <c r="AQ6">
+        <v>-131.0998552821997</v>
       </c>
     </row>
   </sheetData>
